--- a/data/trans_orig/IP24_R_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1565</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4337</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3211</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7181</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2213</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>46692</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43920</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47770</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,99%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>52789</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48819</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54735</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>94,27%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56817</t>
+          <t>47528</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53446</t>
+          <t>43670</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58127</t>
+          <t>49493</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>109606</t>
+          <t>94220</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105689</t>
+          <t>89705</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112428</t>
+          <t>96823</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>48257</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>48257</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>48257</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>56000</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>56000</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>56000</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58571</t>
+          <t>50779</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58571</t>
+          <t>50779</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58571</t>
+          <t>50779</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>114571</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114571</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114571</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10513</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6356</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16082</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8168</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4892</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13012</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7534</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19216</t>
+          <t>13257</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>18711</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14278</t>
+          <t>13094</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28641</t>
+          <t>26154</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>146650</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>141081</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>150807</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,31%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>151131</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>146287</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>154407</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>169959</t>
+          <t>137321</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>162874</t>
+          <t>132261</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>174556</t>
+          <t>140641</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>321090</t>
+          <t>283970</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>312748</t>
+          <t>276527</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>327111</t>
+          <t>289587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157163</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157163</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157163</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182090</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182090</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182090</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341389</t>
+          <t>302681</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341389</t>
+          <t>302681</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341389</t>
+          <t>302681</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28452</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20158</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37921</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,04%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18422</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12509</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30441</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29941</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21554</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42014</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>48363</t>
+          <t>45083</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36886</t>
+          <t>33696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61232</t>
+          <t>55919</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>170711</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>161242</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>179005</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>85,71%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,96%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>154650</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>142631</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>160563</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>89,36%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>181612</t>
+          <t>158041</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169539</t>
+          <t>149598</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>189999</t>
+          <t>163632</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>336262</t>
+          <t>328752</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>323393</t>
+          <t>317916</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>347739</t>
+          <t>340139</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199163</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199163</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199163</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211553</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211553</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211553</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384625</t>
+          <t>373835</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384625</t>
+          <t>373835</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384625</t>
+          <t>373835</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>53790</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>41947</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>67787</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>26046</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17315</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>36242</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>52963</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40332</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66242</t>
+          <t>36094</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>79009</t>
+          <t>80718</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63088</t>
+          <t>66614</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96759</t>
+          <t>98756</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>238855</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>224858</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>250698</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>301</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>249412</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>239216</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>258143</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>90,54%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>252520</t>
+          <t>229625</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>239241</t>
+          <t>220459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>265151</t>
+          <t>237334</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>501931</t>
+          <t>468480</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>484181</t>
+          <t>450442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>517852</t>
+          <t>482584</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>94319</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>79290</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>113187</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>55847</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>44882</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>72726</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>96789</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81121</t>
+          <t>44740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114773</t>
+          <t>67125</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>152636</t>
+          <t>149328</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>131762</t>
+          <t>129735</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174382</t>
+          <t>170692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>602909</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>584041</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>617938</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>83,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>88,63%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>850</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>607982</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>591103</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>618947</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>91,59%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>660908</t>
+          <t>572514</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>642924</t>
+          <t>560397</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>676576</t>
+          <t>582782</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1268890</t>
+          <t>1175422</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1247144</t>
+          <t>1154058</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1289764</t>
+          <t>1195015</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
